--- a/data/education/working/fod_earn_race.xlsx
+++ b/data/education/working/fod_earn_race.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,1694 +498,1626 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Field of Degree</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Total Population </t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>White Alone, Non-Hispanic</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Black Alone, Non-Hispanic</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asian Alone, Non-Hispanic </t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other or Multiple Races, Non-Hispanic </t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hispanic, of Any Race </t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t xml:space="preserve">Population 25 to 64 with a Bachelor's Degree or Higher with earnings </t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>74150</v>
+      </c>
+      <c r="C2" t="n">
+        <v>165.7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>76430</v>
+      </c>
+      <c r="E2" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>62000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>362</v>
+      </c>
+      <c r="H2" t="n">
+        <v>91190</v>
+      </c>
+      <c r="I2" t="n">
+        <v>563.1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>70510</v>
+      </c>
+      <c r="K2" t="n">
+        <v>797.1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>61500</v>
+      </c>
+      <c r="M2" t="n">
+        <v>355.6</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Estimate </t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOE </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Estimate </t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOE </t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Estimate </t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOE </t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Estimate </t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOE </t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Estimate </t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOE </t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Estimate </t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOE </t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science and Engineering Degrees </t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Population 25 to 64 with a Bachelor's Degree or Higher with earnings </t>
+          <t xml:space="preserve">Computer Science </t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74150</v>
+        <v>108500</v>
       </c>
       <c r="C4" t="n">
-        <v>165.7</v>
+        <v>1597</v>
       </c>
       <c r="D4" t="n">
-        <v>76430</v>
+        <v>113600</v>
       </c>
       <c r="E4" t="n">
-        <v>149.4</v>
+        <v>2409</v>
       </c>
       <c r="F4" t="n">
-        <v>62000</v>
+        <v>76950</v>
       </c>
       <c r="G4" t="n">
-        <v>362</v>
+        <v>3757</v>
       </c>
       <c r="H4" t="n">
-        <v>91190</v>
+        <v>120700</v>
       </c>
       <c r="I4" t="n">
-        <v>563.1</v>
+        <v>2408</v>
       </c>
       <c r="J4" t="n">
-        <v>70510</v>
+        <v>104300</v>
       </c>
       <c r="K4" t="n">
-        <v>797.1</v>
+        <v>4868</v>
       </c>
       <c r="L4" t="n">
-        <v>61500</v>
+        <v>86080</v>
       </c>
       <c r="M4" t="n">
-        <v>355.6</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Science and Engineering Degrees </t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t xml:space="preserve">Engineering </t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>100600</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1031</v>
+      </c>
+      <c r="D5" t="n">
+        <v>104400</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1555</v>
+      </c>
+      <c r="F5" t="n">
+        <v>86070</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7068</v>
+      </c>
+      <c r="H5" t="n">
+        <v>110900</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6541</v>
+      </c>
+      <c r="J5" t="n">
+        <v>89810</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>69480</v>
+      </c>
+      <c r="M5" t="n">
+        <v>8901</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computer Science </t>
+          <t xml:space="preserve">Civil Engineering </t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>108500</v>
+        <v>99660</v>
       </c>
       <c r="C6" t="n">
-        <v>1597</v>
+        <v>1702</v>
       </c>
       <c r="D6" t="n">
-        <v>113600</v>
+        <v>104100</v>
       </c>
       <c r="E6" t="n">
-        <v>2409</v>
+        <v>1803</v>
       </c>
       <c r="F6" t="n">
-        <v>76950</v>
+        <v>73580</v>
       </c>
       <c r="G6" t="n">
-        <v>3757</v>
+        <v>8934</v>
       </c>
       <c r="H6" t="n">
-        <v>120700</v>
+        <v>97950</v>
       </c>
       <c r="I6" t="n">
-        <v>2408</v>
+        <v>3772</v>
       </c>
       <c r="J6" t="n">
-        <v>104300</v>
+        <v>91530</v>
       </c>
       <c r="K6" t="n">
-        <v>4868</v>
+        <v>8235</v>
       </c>
       <c r="L6" t="n">
-        <v>86080</v>
+        <v>80660</v>
       </c>
       <c r="M6" t="n">
-        <v>3530</v>
+        <v>4894</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engineering </t>
+          <t xml:space="preserve">Electrical Engineering </t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100600</v>
+        <v>121600</v>
       </c>
       <c r="C7" t="n">
-        <v>1031</v>
+        <v>1239</v>
       </c>
       <c r="D7" t="n">
-        <v>104400</v>
+        <v>124500</v>
       </c>
       <c r="E7" t="n">
-        <v>1555</v>
+        <v>1486</v>
       </c>
       <c r="F7" t="n">
-        <v>86070</v>
+        <v>87920</v>
       </c>
       <c r="G7" t="n">
-        <v>7068</v>
+        <v>10140</v>
       </c>
       <c r="H7" t="n">
-        <v>110900</v>
+        <v>129800</v>
       </c>
       <c r="I7" t="n">
-        <v>6541</v>
+        <v>3076</v>
       </c>
       <c r="J7" t="n">
-        <v>89810</v>
+        <v>114500</v>
       </c>
       <c r="K7" t="n">
-        <v>12000</v>
+        <v>15580</v>
       </c>
       <c r="L7" t="n">
-        <v>69480</v>
+        <v>90580</v>
       </c>
       <c r="M7" t="n">
-        <v>8901</v>
+        <v>4793</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Civil Engineering </t>
+          <t xml:space="preserve">Mechanical Engineering </t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>99660</v>
+        <v>106200</v>
       </c>
       <c r="C8" t="n">
-        <v>1702</v>
+        <v>957.2</v>
       </c>
       <c r="D8" t="n">
-        <v>104100</v>
+        <v>109400</v>
       </c>
       <c r="E8" t="n">
-        <v>1803</v>
+        <v>1988</v>
       </c>
       <c r="F8" t="n">
-        <v>73580</v>
+        <v>85350</v>
       </c>
       <c r="G8" t="n">
-        <v>8934</v>
+        <v>4646</v>
       </c>
       <c r="H8" t="n">
-        <v>97950</v>
+        <v>112700</v>
       </c>
       <c r="I8" t="n">
-        <v>3772</v>
+        <v>3619</v>
       </c>
       <c r="J8" t="n">
-        <v>91530</v>
+        <v>101900</v>
       </c>
       <c r="K8" t="n">
-        <v>8235</v>
+        <v>8043</v>
       </c>
       <c r="L8" t="n">
-        <v>80660</v>
+        <v>84040</v>
       </c>
       <c r="M8" t="n">
-        <v>4894</v>
+        <v>5376</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical Engineering </t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>121600</v>
+        <v>86560</v>
       </c>
       <c r="C9" t="n">
-        <v>1239</v>
+        <v>1476</v>
       </c>
       <c r="D9" t="n">
-        <v>124500</v>
+        <v>89790</v>
       </c>
       <c r="E9" t="n">
-        <v>1486</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="n">
-        <v>87920</v>
+        <v>72510</v>
       </c>
       <c r="G9" t="n">
-        <v>10140</v>
+        <v>7238</v>
       </c>
       <c r="H9" t="n">
-        <v>129800</v>
+        <v>100500</v>
       </c>
       <c r="I9" t="n">
-        <v>3076</v>
+        <v>4737</v>
       </c>
       <c r="J9" t="n">
-        <v>114500</v>
+        <v>91560</v>
       </c>
       <c r="K9" t="n">
-        <v>15580</v>
+        <v>6909</v>
       </c>
       <c r="L9" t="n">
-        <v>90580</v>
+        <v>65330</v>
       </c>
       <c r="M9" t="n">
-        <v>4793</v>
+        <v>5263</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanical Engineering </t>
+          <t xml:space="preserve">Biology </t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>106200</v>
+        <v>81550</v>
       </c>
       <c r="C10" t="n">
-        <v>957.2</v>
+        <v>706.8</v>
       </c>
       <c r="D10" t="n">
-        <v>109400</v>
+        <v>83390</v>
       </c>
       <c r="E10" t="n">
-        <v>1988</v>
+        <v>1109</v>
       </c>
       <c r="F10" t="n">
-        <v>85350</v>
+        <v>63750</v>
       </c>
       <c r="G10" t="n">
-        <v>4646</v>
+        <v>2385</v>
       </c>
       <c r="H10" t="n">
-        <v>112700</v>
+        <v>100100</v>
       </c>
       <c r="I10" t="n">
-        <v>3619</v>
+        <v>5563</v>
       </c>
       <c r="J10" t="n">
-        <v>101900</v>
+        <v>77780</v>
       </c>
       <c r="K10" t="n">
-        <v>8043</v>
+        <v>5144</v>
       </c>
       <c r="L10" t="n">
-        <v>84040</v>
+        <v>69300</v>
       </c>
       <c r="M10" t="n">
-        <v>5376</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t xml:space="preserve">Chemistry </t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>86560</v>
+        <v>94680</v>
       </c>
       <c r="C11" t="n">
-        <v>1476</v>
+        <v>2114</v>
       </c>
       <c r="D11" t="n">
-        <v>89790</v>
+        <v>100400</v>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>2130</v>
       </c>
       <c r="F11" t="n">
-        <v>72510</v>
+        <v>72210</v>
       </c>
       <c r="G11" t="n">
-        <v>7238</v>
+        <v>6923</v>
       </c>
       <c r="H11" t="n">
-        <v>100500</v>
+        <v>101100</v>
       </c>
       <c r="I11" t="n">
-        <v>4737</v>
+        <v>3937</v>
       </c>
       <c r="J11" t="n">
-        <v>91560</v>
+        <v>87240</v>
       </c>
       <c r="K11" t="n">
-        <v>6909</v>
+        <v>11670</v>
       </c>
       <c r="L11" t="n">
-        <v>65330</v>
+        <v>71490</v>
       </c>
       <c r="M11" t="n">
-        <v>5263</v>
+        <v>6386</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biology </t>
+          <t xml:space="preserve">Psychology </t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>81550</v>
+        <v>62270</v>
       </c>
       <c r="C12" t="n">
-        <v>706.8</v>
+        <v>488.2</v>
       </c>
       <c r="D12" t="n">
-        <v>83390</v>
+        <v>64430</v>
       </c>
       <c r="E12" t="n">
-        <v>1109</v>
+        <v>637</v>
       </c>
       <c r="F12" t="n">
-        <v>63750</v>
+        <v>56150</v>
       </c>
       <c r="G12" t="n">
-        <v>2385</v>
+        <v>2314</v>
       </c>
       <c r="H12" t="n">
-        <v>100100</v>
+        <v>73570</v>
       </c>
       <c r="I12" t="n">
-        <v>5563</v>
+        <v>2482</v>
       </c>
       <c r="J12" t="n">
-        <v>77780</v>
+        <v>60480</v>
       </c>
       <c r="K12" t="n">
-        <v>5144</v>
+        <v>1980</v>
       </c>
       <c r="L12" t="n">
-        <v>69300</v>
+        <v>54190</v>
       </c>
       <c r="M12" t="n">
-        <v>3533</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chemistry </t>
+          <t xml:space="preserve">Economics </t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>94680</v>
+        <v>101400</v>
       </c>
       <c r="C13" t="n">
-        <v>2114</v>
+        <v>916.1</v>
       </c>
       <c r="D13" t="n">
-        <v>100400</v>
+        <v>107400</v>
       </c>
       <c r="E13" t="n">
-        <v>2130</v>
+        <v>1438</v>
       </c>
       <c r="F13" t="n">
-        <v>72210</v>
+        <v>73590</v>
       </c>
       <c r="G13" t="n">
-        <v>6923</v>
+        <v>6897</v>
       </c>
       <c r="H13" t="n">
-        <v>101100</v>
+        <v>97230</v>
       </c>
       <c r="I13" t="n">
-        <v>3937</v>
+        <v>5569</v>
       </c>
       <c r="J13" t="n">
-        <v>87240</v>
+        <v>100600</v>
       </c>
       <c r="K13" t="n">
-        <v>11670</v>
+        <v>7658</v>
       </c>
       <c r="L13" t="n">
-        <v>71490</v>
+        <v>76460</v>
       </c>
       <c r="M13" t="n">
-        <v>6386</v>
+        <v>4040</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psychology </t>
+          <t xml:space="preserve">Political Science </t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>62270</v>
+        <v>86380</v>
       </c>
       <c r="C14" t="n">
-        <v>488.2</v>
+        <v>1325</v>
       </c>
       <c r="D14" t="n">
-        <v>64430</v>
+        <v>93760</v>
       </c>
       <c r="E14" t="n">
-        <v>637</v>
+        <v>1752</v>
       </c>
       <c r="F14" t="n">
-        <v>56150</v>
+        <v>63390</v>
       </c>
       <c r="G14" t="n">
-        <v>2314</v>
+        <v>1773</v>
       </c>
       <c r="H14" t="n">
-        <v>73570</v>
+        <v>85540</v>
       </c>
       <c r="I14" t="n">
-        <v>2482</v>
+        <v>6805</v>
       </c>
       <c r="J14" t="n">
-        <v>60480</v>
+        <v>81140</v>
       </c>
       <c r="K14" t="n">
-        <v>1980</v>
+        <v>6556</v>
       </c>
       <c r="L14" t="n">
-        <v>54190</v>
+        <v>71990</v>
       </c>
       <c r="M14" t="n">
-        <v>1400</v>
+        <v>3421</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Economics </t>
+          <t xml:space="preserve">Sociology </t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>101400</v>
+        <v>63660</v>
       </c>
       <c r="C15" t="n">
-        <v>916.1</v>
+        <v>836.9</v>
       </c>
       <c r="D15" t="n">
-        <v>107400</v>
+        <v>66250</v>
       </c>
       <c r="E15" t="n">
-        <v>1438</v>
+        <v>1537</v>
       </c>
       <c r="F15" t="n">
-        <v>73590</v>
+        <v>57660</v>
       </c>
       <c r="G15" t="n">
-        <v>6897</v>
+        <v>2549</v>
       </c>
       <c r="H15" t="n">
-        <v>97230</v>
+        <v>69910</v>
       </c>
       <c r="I15" t="n">
-        <v>5569</v>
+        <v>6088</v>
       </c>
       <c r="J15" t="n">
-        <v>100600</v>
+        <v>66310</v>
       </c>
       <c r="K15" t="n">
-        <v>7658</v>
+        <v>4278</v>
       </c>
       <c r="L15" t="n">
-        <v>76460</v>
+        <v>60340</v>
       </c>
       <c r="M15" t="n">
-        <v>4040</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Political Science </t>
+          <t xml:space="preserve">Nursing </t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>86380</v>
+        <v>79600</v>
       </c>
       <c r="C16" t="n">
-        <v>1325</v>
+        <v>812.7</v>
       </c>
       <c r="D16" t="n">
-        <v>93760</v>
+        <v>78940</v>
       </c>
       <c r="E16" t="n">
-        <v>1752</v>
+        <v>888.7</v>
       </c>
       <c r="F16" t="n">
-        <v>63390</v>
+        <v>80870</v>
       </c>
       <c r="G16" t="n">
-        <v>1773</v>
+        <v>1765</v>
       </c>
       <c r="H16" t="n">
-        <v>85540</v>
+        <v>88390</v>
       </c>
       <c r="I16" t="n">
-        <v>6805</v>
+        <v>3072</v>
       </c>
       <c r="J16" t="n">
-        <v>81140</v>
+        <v>78550</v>
       </c>
       <c r="K16" t="n">
-        <v>6556</v>
+        <v>3200</v>
       </c>
       <c r="L16" t="n">
-        <v>71990</v>
+        <v>70100</v>
       </c>
       <c r="M16" t="n">
-        <v>3421</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sociology </t>
+          <t>Other Science and Engineering Degrees1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>63660</v>
+        <v>77910</v>
       </c>
       <c r="C17" t="n">
-        <v>836.9</v>
+        <v>460.3</v>
       </c>
       <c r="D17" t="n">
-        <v>66250</v>
+        <v>80080</v>
       </c>
       <c r="E17" t="n">
-        <v>1537</v>
+        <v>355.3</v>
       </c>
       <c r="F17" t="n">
-        <v>57660</v>
+        <v>62920</v>
       </c>
       <c r="G17" t="n">
-        <v>2549</v>
+        <v>1137</v>
       </c>
       <c r="H17" t="n">
-        <v>69910</v>
+        <v>98440</v>
       </c>
       <c r="I17" t="n">
-        <v>6088</v>
+        <v>2057</v>
       </c>
       <c r="J17" t="n">
-        <v>66310</v>
+        <v>72820</v>
       </c>
       <c r="K17" t="n">
-        <v>4278</v>
+        <v>1560</v>
       </c>
       <c r="L17" t="n">
-        <v>60340</v>
+        <v>63050</v>
       </c>
       <c r="M17" t="n">
-        <v>2938</v>
+        <v>995.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nursing </t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>79600</v>
-      </c>
-      <c r="C18" t="n">
-        <v>812.7</v>
-      </c>
-      <c r="D18" t="n">
-        <v>78940</v>
-      </c>
-      <c r="E18" t="n">
-        <v>888.7</v>
-      </c>
-      <c r="F18" t="n">
-        <v>80870</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1765</v>
-      </c>
-      <c r="H18" t="n">
-        <v>88390</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3072</v>
-      </c>
-      <c r="J18" t="n">
-        <v>78550</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3200</v>
-      </c>
-      <c r="L18" t="n">
-        <v>70100</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2593</v>
-      </c>
+          <t xml:space="preserve">Business Degrees </t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Other Science and Engineering Degrees1</t>
+          <t xml:space="preserve">General Business </t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>77910</v>
+        <v>80120</v>
       </c>
       <c r="C19" t="n">
-        <v>460.3</v>
+        <v>710.7</v>
       </c>
       <c r="D19" t="n">
-        <v>80080</v>
+        <v>85100</v>
       </c>
       <c r="E19" t="n">
-        <v>355.3</v>
+        <v>905.3</v>
       </c>
       <c r="F19" t="n">
-        <v>62920</v>
+        <v>60690</v>
       </c>
       <c r="G19" t="n">
-        <v>1137</v>
+        <v>2015</v>
       </c>
       <c r="H19" t="n">
-        <v>98440</v>
+        <v>75650</v>
       </c>
       <c r="I19" t="n">
-        <v>2057</v>
+        <v>2936</v>
       </c>
       <c r="J19" t="n">
-        <v>72820</v>
+        <v>80320</v>
       </c>
       <c r="K19" t="n">
-        <v>1560</v>
+        <v>3975</v>
       </c>
       <c r="L19" t="n">
-        <v>63050</v>
+        <v>65900</v>
       </c>
       <c r="M19" t="n">
-        <v>995.7</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Degrees </t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+          <t xml:space="preserve">Accounting </t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>84880</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1051</v>
+      </c>
+      <c r="D20" t="n">
+        <v>94720</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1128</v>
+      </c>
+      <c r="F20" t="n">
+        <v>67070</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2605</v>
+      </c>
+      <c r="H20" t="n">
+        <v>78490</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3572</v>
+      </c>
+      <c r="J20" t="n">
+        <v>81870</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3291</v>
+      </c>
+      <c r="L20" t="n">
+        <v>62550</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1772</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">General Business </t>
+          <t xml:space="preserve">Business Management and Adminstration </t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>80120</v>
+        <v>75600</v>
       </c>
       <c r="C21" t="n">
-        <v>710.7</v>
+        <v>581.2</v>
       </c>
       <c r="D21" t="n">
-        <v>85100</v>
+        <v>82290</v>
       </c>
       <c r="E21" t="n">
-        <v>905.3</v>
+        <v>599.1</v>
       </c>
       <c r="F21" t="n">
-        <v>60690</v>
+        <v>61890</v>
       </c>
       <c r="G21" t="n">
-        <v>2015</v>
+        <v>1127</v>
       </c>
       <c r="H21" t="n">
-        <v>75650</v>
+        <v>75610</v>
       </c>
       <c r="I21" t="n">
-        <v>2936</v>
+        <v>2604</v>
       </c>
       <c r="J21" t="n">
-        <v>80320</v>
+        <v>71910</v>
       </c>
       <c r="K21" t="n">
-        <v>3975</v>
+        <v>2148</v>
       </c>
       <c r="L21" t="n">
-        <v>65900</v>
+        <v>59780</v>
       </c>
       <c r="M21" t="n">
-        <v>3280</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accounting </t>
+          <t xml:space="preserve">Marketing </t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>84880</v>
+        <v>75930</v>
       </c>
       <c r="C22" t="n">
-        <v>1051</v>
+        <v>798.6</v>
       </c>
       <c r="D22" t="n">
-        <v>94720</v>
+        <v>80700</v>
       </c>
       <c r="E22" t="n">
-        <v>1128</v>
+        <v>875.8</v>
       </c>
       <c r="F22" t="n">
-        <v>67070</v>
+        <v>63060</v>
       </c>
       <c r="G22" t="n">
-        <v>2605</v>
+        <v>2619</v>
       </c>
       <c r="H22" t="n">
-        <v>78490</v>
+        <v>71200</v>
       </c>
       <c r="I22" t="n">
-        <v>3572</v>
+        <v>4219</v>
       </c>
       <c r="J22" t="n">
-        <v>81870</v>
+        <v>72780</v>
       </c>
       <c r="K22" t="n">
-        <v>3291</v>
+        <v>4193</v>
       </c>
       <c r="L22" t="n">
-        <v>62550</v>
+        <v>60910</v>
       </c>
       <c r="M22" t="n">
-        <v>1772</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Management and Adminstration </t>
+          <t xml:space="preserve">Finance </t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>75600</v>
+        <v>99900</v>
       </c>
       <c r="C23" t="n">
-        <v>581.2</v>
+        <v>1779</v>
       </c>
       <c r="D23" t="n">
-        <v>82290</v>
+        <v>105000</v>
       </c>
       <c r="E23" t="n">
-        <v>599.1</v>
+        <v>1019</v>
       </c>
       <c r="F23" t="n">
-        <v>61890</v>
+        <v>74440</v>
       </c>
       <c r="G23" t="n">
-        <v>1127</v>
+        <v>3790</v>
       </c>
       <c r="H23" t="n">
-        <v>75610</v>
+        <v>93120</v>
       </c>
       <c r="I23" t="n">
-        <v>2604</v>
+        <v>4593</v>
       </c>
       <c r="J23" t="n">
-        <v>71910</v>
+        <v>100200</v>
       </c>
       <c r="K23" t="n">
-        <v>2148</v>
+        <v>12670</v>
       </c>
       <c r="L23" t="n">
-        <v>59780</v>
+        <v>77430</v>
       </c>
       <c r="M23" t="n">
-        <v>1644</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marketing </t>
+          <t xml:space="preserve">Other Business Degrees </t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>75930</v>
+        <v>77160</v>
       </c>
       <c r="C24" t="n">
-        <v>798.6</v>
+        <v>882.2</v>
       </c>
       <c r="D24" t="n">
-        <v>80700</v>
+        <v>83460</v>
       </c>
       <c r="E24" t="n">
-        <v>875.8</v>
+        <v>1400</v>
       </c>
       <c r="F24" t="n">
-        <v>63060</v>
+        <v>63500</v>
       </c>
       <c r="G24" t="n">
-        <v>2619</v>
+        <v>2656</v>
       </c>
       <c r="H24" t="n">
-        <v>71200</v>
+        <v>75220</v>
       </c>
       <c r="I24" t="n">
-        <v>4219</v>
+        <v>4646</v>
       </c>
       <c r="J24" t="n">
-        <v>72780</v>
+        <v>76730</v>
       </c>
       <c r="K24" t="n">
-        <v>4193</v>
+        <v>6051</v>
       </c>
       <c r="L24" t="n">
-        <v>60910</v>
+        <v>61270</v>
       </c>
       <c r="M24" t="n">
-        <v>2219</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finance </t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>99900</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1779</v>
-      </c>
-      <c r="D25" t="n">
-        <v>105000</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1019</v>
-      </c>
-      <c r="F25" t="n">
-        <v>74440</v>
-      </c>
-      <c r="G25" t="n">
-        <v>3790</v>
-      </c>
-      <c r="H25" t="n">
-        <v>93120</v>
-      </c>
-      <c r="I25" t="n">
-        <v>4593</v>
-      </c>
-      <c r="J25" t="n">
-        <v>100200</v>
-      </c>
-      <c r="K25" t="n">
-        <v>12670</v>
-      </c>
-      <c r="L25" t="n">
-        <v>77430</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4038</v>
-      </c>
+          <t xml:space="preserve">Education Degrees </t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Business Degrees </t>
+          <t>General Education</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>77160</v>
+        <v>58000</v>
       </c>
       <c r="C26" t="n">
-        <v>882.2</v>
+        <v>730.8</v>
       </c>
       <c r="D26" t="n">
-        <v>83460</v>
+        <v>59870</v>
       </c>
       <c r="E26" t="n">
-        <v>1400</v>
+        <v>689.2</v>
       </c>
       <c r="F26" t="n">
-        <v>63500</v>
+        <v>54740</v>
       </c>
       <c r="G26" t="n">
-        <v>2656</v>
+        <v>1636</v>
       </c>
       <c r="H26" t="n">
-        <v>75220</v>
+        <v>58580</v>
       </c>
       <c r="I26" t="n">
-        <v>4646</v>
+        <v>4667</v>
       </c>
       <c r="J26" t="n">
-        <v>76730</v>
+        <v>56420</v>
       </c>
       <c r="K26" t="n">
-        <v>6051</v>
+        <v>2543</v>
       </c>
       <c r="L26" t="n">
-        <v>61270</v>
+        <v>52110</v>
       </c>
       <c r="M26" t="n">
-        <v>1640</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Education Degrees </t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+          <t>Elementary Education</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>54900</v>
+      </c>
+      <c r="C27" t="n">
+        <v>549.8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>55100</v>
+      </c>
+      <c r="E27" t="n">
+        <v>554.2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>60010</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2596</v>
+      </c>
+      <c r="H27" t="n">
+        <v>51170</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2302</v>
+      </c>
+      <c r="J27" t="n">
+        <v>52230</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2307</v>
+      </c>
+      <c r="L27" t="n">
+        <v>52920</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2113</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>General Education</t>
+          <t>Other Education Degrees</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>58000</v>
+        <v>58120</v>
       </c>
       <c r="C28" t="n">
-        <v>730.8</v>
+        <v>477.6</v>
       </c>
       <c r="D28" t="n">
-        <v>59870</v>
+        <v>59000</v>
       </c>
       <c r="E28" t="n">
-        <v>689.2</v>
+        <v>491.7</v>
       </c>
       <c r="F28" t="n">
-        <v>54740</v>
+        <v>56360</v>
       </c>
       <c r="G28" t="n">
-        <v>1636</v>
+        <v>1662</v>
       </c>
       <c r="H28" t="n">
-        <v>58580</v>
+        <v>56240</v>
       </c>
       <c r="I28" t="n">
-        <v>4667</v>
+        <v>3802</v>
       </c>
       <c r="J28" t="n">
-        <v>56420</v>
+        <v>55700</v>
       </c>
       <c r="K28" t="n">
-        <v>2543</v>
+        <v>1775</v>
       </c>
       <c r="L28" t="n">
-        <v>52110</v>
+        <v>53320</v>
       </c>
       <c r="M28" t="n">
-        <v>1323</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Elementary Education</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>54900</v>
-      </c>
-      <c r="C29" t="n">
-        <v>549.8</v>
-      </c>
-      <c r="D29" t="n">
-        <v>55100</v>
-      </c>
-      <c r="E29" t="n">
-        <v>554.2</v>
-      </c>
-      <c r="F29" t="n">
-        <v>60010</v>
-      </c>
-      <c r="G29" t="n">
-        <v>2596</v>
-      </c>
-      <c r="H29" t="n">
-        <v>51170</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2302</v>
-      </c>
-      <c r="J29" t="n">
-        <v>52230</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2307</v>
-      </c>
-      <c r="L29" t="n">
-        <v>52920</v>
-      </c>
-      <c r="M29" t="n">
-        <v>2113</v>
-      </c>
+          <t xml:space="preserve">Arts, Humanities and Other Degrees </t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Other Education Degrees</t>
+          <t xml:space="preserve">Communications </t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>58120</v>
+        <v>67840</v>
       </c>
       <c r="C30" t="n">
-        <v>477.6</v>
+        <v>1017</v>
       </c>
       <c r="D30" t="n">
-        <v>59000</v>
+        <v>71290</v>
       </c>
       <c r="E30" t="n">
-        <v>491.7</v>
+        <v>982.7</v>
       </c>
       <c r="F30" t="n">
-        <v>56360</v>
+        <v>59010</v>
       </c>
       <c r="G30" t="n">
-        <v>1662</v>
+        <v>2692</v>
       </c>
       <c r="H30" t="n">
-        <v>56240</v>
+        <v>74680</v>
       </c>
       <c r="I30" t="n">
-        <v>3802</v>
+        <v>3871</v>
       </c>
       <c r="J30" t="n">
-        <v>55700</v>
+        <v>62330</v>
       </c>
       <c r="K30" t="n">
-        <v>1775</v>
+        <v>3002</v>
       </c>
       <c r="L30" t="n">
-        <v>53320</v>
+        <v>60240</v>
       </c>
       <c r="M30" t="n">
-        <v>1649</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arts, Humanities and Other Degrees </t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+          <t xml:space="preserve">English Language and Literature </t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>65060</v>
+      </c>
+      <c r="C31" t="n">
+        <v>927</v>
+      </c>
+      <c r="D31" t="n">
+        <v>66990</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1161</v>
+      </c>
+      <c r="F31" t="n">
+        <v>61750</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2781</v>
+      </c>
+      <c r="H31" t="n">
+        <v>64800</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3472</v>
+      </c>
+      <c r="J31" t="n">
+        <v>63070</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3208</v>
+      </c>
+      <c r="L31" t="n">
+        <v>56890</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2545</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communications </t>
+          <t xml:space="preserve">Liberal Arts </t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>67840</v>
+        <v>61380</v>
       </c>
       <c r="C32" t="n">
-        <v>1017</v>
+        <v>1044</v>
       </c>
       <c r="D32" t="n">
-        <v>71290</v>
+        <v>63780</v>
       </c>
       <c r="E32" t="n">
-        <v>982.7</v>
+        <v>1152</v>
       </c>
       <c r="F32" t="n">
-        <v>59010</v>
+        <v>49270</v>
       </c>
       <c r="G32" t="n">
-        <v>2692</v>
+        <v>3446</v>
       </c>
       <c r="H32" t="n">
-        <v>74680</v>
+        <v>60920</v>
       </c>
       <c r="I32" t="n">
-        <v>3871</v>
+        <v>5993</v>
       </c>
       <c r="J32" t="n">
-        <v>62330</v>
+        <v>58740</v>
       </c>
       <c r="K32" t="n">
-        <v>3002</v>
+        <v>5733</v>
       </c>
       <c r="L32" t="n">
-        <v>60240</v>
+        <v>58410</v>
       </c>
       <c r="M32" t="n">
-        <v>2470</v>
+        <v>2994</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">English Language and Literature </t>
+          <t xml:space="preserve">History </t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>65060</v>
+        <v>73560</v>
       </c>
       <c r="C33" t="n">
-        <v>927</v>
+        <v>1006</v>
       </c>
       <c r="D33" t="n">
-        <v>66990</v>
+        <v>76100</v>
       </c>
       <c r="E33" t="n">
-        <v>1161</v>
+        <v>1141</v>
       </c>
       <c r="F33" t="n">
-        <v>61750</v>
+        <v>62710</v>
       </c>
       <c r="G33" t="n">
-        <v>2781</v>
+        <v>2199</v>
       </c>
       <c r="H33" t="n">
-        <v>64800</v>
+        <v>72590</v>
       </c>
       <c r="I33" t="n">
-        <v>3472</v>
+        <v>7341</v>
       </c>
       <c r="J33" t="n">
-        <v>63070</v>
+        <v>68010</v>
       </c>
       <c r="K33" t="n">
-        <v>3208</v>
+        <v>6212</v>
       </c>
       <c r="L33" t="n">
-        <v>56890</v>
+        <v>63690</v>
       </c>
       <c r="M33" t="n">
-        <v>2545</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liberal Arts </t>
+          <t xml:space="preserve">Fine Arts </t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>61380</v>
+        <v>53450</v>
       </c>
       <c r="C34" t="n">
-        <v>1044</v>
+        <v>1303</v>
       </c>
       <c r="D34" t="n">
-        <v>63780</v>
+        <v>54340</v>
       </c>
       <c r="E34" t="n">
-        <v>1152</v>
+        <v>1803</v>
       </c>
       <c r="F34" t="n">
-        <v>49270</v>
+        <v>47470</v>
       </c>
       <c r="G34" t="n">
-        <v>3446</v>
+        <v>5006</v>
       </c>
       <c r="H34" t="n">
-        <v>60920</v>
+        <v>60970</v>
       </c>
       <c r="I34" t="n">
-        <v>5993</v>
+        <v>5181</v>
       </c>
       <c r="J34" t="n">
-        <v>58740</v>
+        <v>55840</v>
       </c>
       <c r="K34" t="n">
-        <v>5733</v>
+        <v>4477</v>
       </c>
       <c r="L34" t="n">
-        <v>58410</v>
+        <v>47340</v>
       </c>
       <c r="M34" t="n">
-        <v>2994</v>
+        <v>3206</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">History </t>
+          <t xml:space="preserve">Commerical Art and Graphic Design </t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>73560</v>
+        <v>59770</v>
       </c>
       <c r="C35" t="n">
-        <v>1006</v>
+        <v>1049</v>
       </c>
       <c r="D35" t="n">
-        <v>76100</v>
+        <v>61930</v>
       </c>
       <c r="E35" t="n">
-        <v>1141</v>
+        <v>1022</v>
       </c>
       <c r="F35" t="n">
-        <v>62710</v>
+        <v>52240</v>
       </c>
       <c r="G35" t="n">
-        <v>2199</v>
+        <v>2693</v>
       </c>
       <c r="H35" t="n">
-        <v>72590</v>
+        <v>63190</v>
       </c>
       <c r="I35" t="n">
-        <v>7341</v>
+        <v>2653</v>
       </c>
       <c r="J35" t="n">
-        <v>68010</v>
+        <v>53630</v>
       </c>
       <c r="K35" t="n">
-        <v>6212</v>
+        <v>2707</v>
       </c>
       <c r="L35" t="n">
-        <v>63690</v>
+        <v>50870</v>
       </c>
       <c r="M35" t="n">
-        <v>2482</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fine Arts </t>
+          <t xml:space="preserve">Family and Consumer Sciences </t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>53450</v>
+        <v>52850</v>
       </c>
       <c r="C36" t="n">
-        <v>1303</v>
+        <v>951.6</v>
       </c>
       <c r="D36" t="n">
-        <v>54340</v>
+        <v>53020</v>
       </c>
       <c r="E36" t="n">
-        <v>1803</v>
+        <v>1182</v>
       </c>
       <c r="F36" t="n">
-        <v>47470</v>
+        <v>51220</v>
       </c>
       <c r="G36" t="n">
-        <v>5006</v>
+        <v>2286</v>
       </c>
       <c r="H36" t="n">
-        <v>60970</v>
+        <v>62000</v>
       </c>
       <c r="I36" t="n">
-        <v>5181</v>
+        <v>3520</v>
       </c>
       <c r="J36" t="n">
-        <v>55840</v>
+        <v>51860</v>
       </c>
       <c r="K36" t="n">
-        <v>4477</v>
+        <v>3839</v>
       </c>
       <c r="L36" t="n">
-        <v>47340</v>
+        <v>49620</v>
       </c>
       <c r="M36" t="n">
-        <v>3206</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commerical Art and Graphic Design </t>
+          <t>Physical Fitness, Parks, Recreation, and Leisure</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>59770</v>
+        <v>61580</v>
       </c>
       <c r="C37" t="n">
-        <v>1049</v>
+        <v>691.3</v>
       </c>
       <c r="D37" t="n">
-        <v>61930</v>
+        <v>63520</v>
       </c>
       <c r="E37" t="n">
-        <v>1022</v>
+        <v>947.7</v>
       </c>
       <c r="F37" t="n">
-        <v>52240</v>
+        <v>51530</v>
       </c>
       <c r="G37" t="n">
-        <v>2693</v>
+        <v>2914</v>
       </c>
       <c r="H37" t="n">
-        <v>63190</v>
+        <v>64900</v>
       </c>
       <c r="I37" t="n">
-        <v>2653</v>
+        <v>3710</v>
       </c>
       <c r="J37" t="n">
-        <v>53630</v>
+        <v>63370</v>
       </c>
       <c r="K37" t="n">
-        <v>2707</v>
+        <v>4694</v>
       </c>
       <c r="L37" t="n">
-        <v>50870</v>
+        <v>52080</v>
       </c>
       <c r="M37" t="n">
-        <v>2641</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Family and Consumer Sciences </t>
+          <t>Criminal Justice and Fire Protection</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>52850</v>
+        <v>64690</v>
       </c>
       <c r="C38" t="n">
-        <v>951.6</v>
+        <v>809.2</v>
       </c>
       <c r="D38" t="n">
-        <v>53020</v>
+        <v>70370</v>
       </c>
       <c r="E38" t="n">
-        <v>1182</v>
+        <v>1104</v>
       </c>
       <c r="F38" t="n">
-        <v>51220</v>
+        <v>57480</v>
       </c>
       <c r="G38" t="n">
-        <v>2286</v>
+        <v>2290</v>
       </c>
       <c r="H38" t="n">
-        <v>62000</v>
+        <v>69320</v>
       </c>
       <c r="I38" t="n">
-        <v>3520</v>
+        <v>4027</v>
       </c>
       <c r="J38" t="n">
-        <v>51860</v>
+        <v>62320</v>
       </c>
       <c r="K38" t="n">
-        <v>3839</v>
+        <v>2035</v>
       </c>
       <c r="L38" t="n">
-        <v>49620</v>
+        <v>57930</v>
       </c>
       <c r="M38" t="n">
-        <v>3152</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Physical Fitness, Parks, Recreation, and Leisure</t>
+          <t xml:space="preserve">Social Work </t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>61580</v>
+        <v>55060</v>
       </c>
       <c r="C39" t="n">
-        <v>691.3</v>
+        <v>838</v>
       </c>
       <c r="D39" t="n">
-        <v>63520</v>
+        <v>56040</v>
       </c>
       <c r="E39" t="n">
-        <v>947.7</v>
+        <v>1051</v>
       </c>
       <c r="F39" t="n">
-        <v>51530</v>
+        <v>54160</v>
       </c>
       <c r="G39" t="n">
-        <v>2914</v>
+        <v>2498</v>
       </c>
       <c r="H39" t="n">
-        <v>64900</v>
+        <v>61930</v>
       </c>
       <c r="I39" t="n">
-        <v>3710</v>
+        <v>5628</v>
       </c>
       <c r="J39" t="n">
-        <v>63370</v>
+        <v>53330</v>
       </c>
       <c r="K39" t="n">
-        <v>4694</v>
+        <v>1904</v>
       </c>
       <c r="L39" t="n">
-        <v>52080</v>
+        <v>52120</v>
       </c>
       <c r="M39" t="n">
-        <v>2490</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Criminal Justice and Fire Protection</t>
+          <t xml:space="preserve">Other Degrees </t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>64690</v>
+        <v>62100</v>
       </c>
       <c r="C40" t="n">
-        <v>809.2</v>
+        <v>419.6</v>
       </c>
       <c r="D40" t="n">
-        <v>70370</v>
+        <v>64550</v>
       </c>
       <c r="E40" t="n">
-        <v>1104</v>
+        <v>498.9</v>
       </c>
       <c r="F40" t="n">
-        <v>57480</v>
+        <v>53780</v>
       </c>
       <c r="G40" t="n">
-        <v>2290</v>
+        <v>1343</v>
       </c>
       <c r="H40" t="n">
-        <v>69320</v>
+        <v>60350</v>
       </c>
       <c r="I40" t="n">
-        <v>4027</v>
+        <v>2190</v>
       </c>
       <c r="J40" t="n">
-        <v>62320</v>
+        <v>60740</v>
       </c>
       <c r="K40" t="n">
-        <v>2035</v>
+        <v>1485</v>
       </c>
       <c r="L40" t="n">
-        <v>57930</v>
+        <v>53090</v>
       </c>
       <c r="M40" t="n">
-        <v>2397</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Social Work </t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>55060</v>
-      </c>
-      <c r="C41" t="n">
-        <v>838</v>
-      </c>
-      <c r="D41" t="n">
-        <v>56040</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1051</v>
-      </c>
-      <c r="F41" t="n">
-        <v>54160</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2498</v>
-      </c>
-      <c r="H41" t="n">
-        <v>61930</v>
-      </c>
-      <c r="I41" t="n">
-        <v>5628</v>
-      </c>
-      <c r="J41" t="n">
-        <v>53330</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1904</v>
-      </c>
-      <c r="L41" t="n">
-        <v>52120</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1691</v>
-      </c>
+          <t>Source: U.S. Census Bureau, 2022 American Community Survey, 1-year estimates. For more information, refer to &lt;www.census.gov/acs&gt;.</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Degrees </t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>62100</v>
-      </c>
-      <c r="C42" t="n">
-        <v>419.6</v>
-      </c>
-      <c r="D42" t="n">
-        <v>64550</v>
-      </c>
-      <c r="E42" t="n">
-        <v>498.9</v>
-      </c>
-      <c r="F42" t="n">
-        <v>53780</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1343</v>
-      </c>
-      <c r="H42" t="n">
-        <v>60350</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2190</v>
-      </c>
-      <c r="J42" t="n">
-        <v>60740</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1485</v>
-      </c>
-      <c r="L42" t="n">
-        <v>53090</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1381</v>
-      </c>
+          <t>The Census Bureau has reviewed this data product to ensure appropriate access, use, and disclosure avoidance protection of the confidential source data used to produce this product (Data Management System (DMS) number: P-001-0000001262, Disclosure Review Board (DRB) approval number: CBDRB-FY23-SEHSD003-068.</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Source: U.S. Census Bureau, 2022 American Community Survey, 1-year estimates. For more information, refer to &lt;www.census.gov/acs&gt;.</t>
+          <t>Note: 1. Science and Engineering related fields are included within the "other science and engineering degrees" category.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2201,44 +2133,6 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>The Census Bureau has reviewed this data product to ensure appropriate access, use, and disclosure avoidance protection of the confidential source data used to produce this product (Data Management System (DMS) number: P-001-0000001262, Disclosure Review Board (DRB) approval number: CBDRB-FY23-SEHSD003-068.</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Note: 1. Science and Engineering related fields are included within the "other science and engineering degrees" category.</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
